--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_insurance_life.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06035</v>
+        <v>0.030545</v>
       </c>
       <c r="G2">
-        <v>0.01807427785419532</v>
+        <v>-0.002876254180602007</v>
       </c>
       <c r="H2">
-        <v>0.01807427785419532</v>
+        <v>-0.002876254180602007</v>
       </c>
       <c r="I2">
-        <v>-0.01993669738177937</v>
+        <v>-0.005565675833721604</v>
       </c>
       <c r="J2">
-        <v>-0.01993669738177937</v>
+        <v>-0.005565675833721604</v>
       </c>
       <c r="K2">
-        <v>-3.903</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="L2">
-        <v>-0.02684319119669876</v>
+        <v>-0.007190635451505016</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,55 +630,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>32.02</v>
+        <v>12.69</v>
       </c>
       <c r="V2">
-        <v>0.3802850356294537</v>
+        <v>0.1650195058517555</v>
       </c>
       <c r="W2">
-        <v>-0.05739705882352941</v>
+        <v>-0.01708971886735004</v>
       </c>
       <c r="X2">
-        <v>0.06116896988414777</v>
+        <v>0.09882656322937278</v>
       </c>
       <c r="Y2">
-        <v>-0.1185660287076772</v>
+        <v>-0.1159162820967228</v>
       </c>
       <c r="Z2">
-        <v>3.735966455154839</v>
+        <v>3.223869647440852</v>
       </c>
       <c r="AA2">
-        <v>-0.07053878760296378</v>
+        <v>-0.07981983925230346</v>
       </c>
       <c r="AB2">
-        <v>0.05852547977323531</v>
+        <v>0.09504041897683543</v>
       </c>
       <c r="AC2">
-        <v>-0.1290642673761991</v>
+        <v>-0.1748602582291389</v>
       </c>
       <c r="AD2">
-        <v>6.19</v>
+        <v>5.05</v>
       </c>
       <c r="AE2">
-        <v>0.0289789965536019</v>
+        <v>0.02827414856551929</v>
       </c>
       <c r="AF2">
-        <v>6.218978996553602</v>
+        <v>5.078274148565519</v>
       </c>
       <c r="AG2">
-        <v>-25.8010210034464</v>
+        <v>-7.611725851434482</v>
       </c>
       <c r="AH2">
-        <v>0.06877957554453965</v>
+        <v>0.06194658525455649</v>
       </c>
       <c r="AI2">
-        <v>0.08997498352606874</v>
+        <v>0.07256929683324603</v>
       </c>
       <c r="AJ2">
-        <v>-0.4418060289199413</v>
+        <v>-0.1098559019541125</v>
       </c>
       <c r="AK2">
-        <v>-0.6954644494621605</v>
+        <v>-0.1328670825672809</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -687,10 +687,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>-3.175987685992817</v>
+        <v>15.3030303030303</v>
       </c>
       <c r="AP2">
-        <v>13.23808158206588</v>
+        <v>-23.06583591343782</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AXA Green Crescent Insurance Company PJSC (ADX:AXAGCIC)</t>
+          <t>HAYAH Insurance Company P.J.S.C. (ADX:HAYAH)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,25 +710,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.06709999999999999</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="G3">
-        <v>0.05722222222222222</v>
+        <v>0.02546153846153846</v>
       </c>
       <c r="H3">
-        <v>0.05722222222222222</v>
+        <v>0.02546153846153846</v>
       </c>
       <c r="I3">
-        <v>-0.06694444444444443</v>
+        <v>0.09769230769230769</v>
       </c>
       <c r="J3">
-        <v>-0.06694444444444443</v>
+        <v>0.09769230769230769</v>
       </c>
       <c r="K3">
-        <v>-0.723</v>
+        <v>1.27</v>
       </c>
       <c r="L3">
-        <v>-0.06694444444444443</v>
+        <v>0.09769230769230769</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,7 +737,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,37 +746,37 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.72</v>
+        <v>3.2</v>
       </c>
       <c r="V3">
-        <v>0.1606741573033708</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="W3">
-        <v>-0.02126470588235294</v>
+        <v>0.03802395209580839</v>
       </c>
       <c r="X3">
-        <v>0.05987969226530488</v>
+        <v>0.09310506888394895</v>
       </c>
       <c r="Y3">
-        <v>-0.08114439814765782</v>
+        <v>-0.05508111678814057</v>
       </c>
       <c r="Z3">
-        <v>0.9</v>
+        <v>0.4696531791907514</v>
       </c>
       <c r="AA3">
-        <v>-0.06025</v>
+        <v>0.04588150289017341</v>
       </c>
       <c r="AB3">
-        <v>0.05987969226530488</v>
+        <v>0.09310506888394895</v>
       </c>
       <c r="AC3">
-        <v>-0.1201296922653049</v>
+        <v>-0.04722356599377554</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-5.72</v>
+        <v>-3.2</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -797,10 +797,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.1914323962516733</v>
+        <v>-0.06451612903225808</v>
       </c>
       <c r="AK3">
-        <v>-0.2066473988439306</v>
+        <v>-0.106312292358804</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -809,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>7.955493741307372</v>
+        <v>-2.388059701492537</v>
       </c>
     </row>
     <row r="4">
@@ -832,25 +832,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0536</v>
+        <v>0.009689999999999999</v>
       </c>
       <c r="G4">
-        <v>0.01493313521545319</v>
+        <v>-0.006332082551594747</v>
       </c>
       <c r="H4">
-        <v>0.01493313521545319</v>
+        <v>-0.006332082551594747</v>
       </c>
       <c r="I4">
-        <v>-0.01616490192652838</v>
+        <v>-0.01815811284909103</v>
       </c>
       <c r="J4">
-        <v>-0.01616490192652838</v>
+        <v>-0.01815811284909103</v>
       </c>
       <c r="K4">
-        <v>-3.18</v>
+        <v>-2.13</v>
       </c>
       <c r="L4">
-        <v>-0.02362555720653789</v>
+        <v>-0.0199812382739212</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -874,55 +874,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>26.3</v>
+        <v>9.49</v>
       </c>
       <c r="V4">
-        <v>0.5411522633744856</v>
+        <v>0.3937759336099585</v>
       </c>
       <c r="W4">
-        <v>-0.09352941176470589</v>
+        <v>-0.07220338983050847</v>
       </c>
       <c r="X4">
-        <v>0.06245824750299066</v>
+        <v>0.1045480575747966</v>
       </c>
       <c r="Y4">
-        <v>-0.1559876592676966</v>
+        <v>-0.1767514474053051</v>
       </c>
       <c r="Z4">
-        <v>5.000189643791194</v>
+        <v>11.31842185929957</v>
       </c>
       <c r="AA4">
-        <v>-0.08082757520592757</v>
+        <v>-0.2055211813947803</v>
       </c>
       <c r="AB4">
-        <v>0.05717126728116575</v>
+        <v>0.0969757690697219</v>
       </c>
       <c r="AC4">
-        <v>-0.1379988424870933</v>
+        <v>-0.3024969504645023</v>
       </c>
       <c r="AD4">
-        <v>6.19</v>
+        <v>5.05</v>
       </c>
       <c r="AE4">
-        <v>0.0289789965536019</v>
+        <v>0.02827414856551929</v>
       </c>
       <c r="AF4">
-        <v>6.218978996553602</v>
+        <v>5.078274148565519</v>
       </c>
       <c r="AG4">
-        <v>-20.0810210034464</v>
+        <v>-4.411725851434481</v>
       </c>
       <c r="AH4">
-        <v>0.113445728293199</v>
+        <v>0.1740429924919045</v>
       </c>
       <c r="AI4">
-        <v>0.1741085319698989</v>
+        <v>0.1384545556313786</v>
       </c>
       <c r="AJ4">
-        <v>-0.7041283282221675</v>
+        <v>-0.2240788511041694</v>
       </c>
       <c r="AK4">
-        <v>-2.13197428413356</v>
+        <v>-0.1622657557198145</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -931,10 +931,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-5.032520325203253</v>
+        <v>-5</v>
       </c>
       <c r="AP4">
-        <v>16.32603333613528</v>
+        <v>4.368045397459882</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_insurance_life.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.030545</v>
+        <v>0.0173</v>
       </c>
       <c r="G2">
-        <v>-0.002876254180602007</v>
+        <v>0.0292410119840213</v>
       </c>
       <c r="H2">
-        <v>-0.002876254180602007</v>
+        <v>0.0292410119840213</v>
       </c>
       <c r="I2">
-        <v>-0.005565675833721604</v>
+        <v>-0.1945264343304508</v>
       </c>
       <c r="J2">
-        <v>-0.005565675833721604</v>
+        <v>-0.1945264343304508</v>
       </c>
       <c r="K2">
-        <v>-0.8599999999999999</v>
+        <v>-14.29</v>
       </c>
       <c r="L2">
-        <v>-0.007190635451505016</v>
+        <v>-0.1902796271637816</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,55 +630,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>12.69</v>
+        <v>16.19</v>
       </c>
       <c r="V2">
-        <v>0.1650195058517555</v>
+        <v>0.2316165951359084</v>
       </c>
       <c r="W2">
-        <v>-0.01708971886735004</v>
+        <v>-0.2251463488805261</v>
       </c>
       <c r="X2">
-        <v>0.09882656322937278</v>
+        <v>0.08032001382291871</v>
       </c>
       <c r="Y2">
-        <v>-0.1159162820967228</v>
+        <v>-0.3054663627034448</v>
       </c>
       <c r="Z2">
-        <v>3.223869647440852</v>
+        <v>1.309396288468871</v>
       </c>
       <c r="AA2">
-        <v>-0.07981983925230346</v>
+        <v>-0.2659441928402089</v>
       </c>
       <c r="AB2">
-        <v>0.09504041897683543</v>
+        <v>0.08020754940940113</v>
       </c>
       <c r="AC2">
-        <v>-0.1748602582291389</v>
+        <v>-0.34615174224961</v>
       </c>
       <c r="AD2">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>0.02827414856551929</v>
+        <v>0.09467609108425908</v>
       </c>
       <c r="AF2">
-        <v>5.078274148565519</v>
+        <v>0.09467609108425908</v>
       </c>
       <c r="AG2">
-        <v>-7.611725851434482</v>
+        <v>-16.09532390891574</v>
       </c>
       <c r="AH2">
-        <v>0.06194658525455649</v>
+        <v>0.001352618461453509</v>
       </c>
       <c r="AI2">
-        <v>0.07256929683324603</v>
+        <v>0.002311728479397493</v>
       </c>
       <c r="AJ2">
-        <v>-0.1098559019541125</v>
+        <v>-0.2991435889636891</v>
       </c>
       <c r="AK2">
-        <v>-0.1328670825672809</v>
+        <v>-0.6499307259144954</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -687,10 +687,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>15.3030303030303</v>
+        <v>-0</v>
       </c>
       <c r="AP2">
-        <v>-23.06583591343782</v>
+        <v>1.112323697920922</v>
       </c>
     </row>
     <row r="3">
@@ -710,25 +710,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.05139999999999999</v>
+        <v>0.127</v>
       </c>
       <c r="G3">
-        <v>0.02546153846153846</v>
+        <v>0.05224043715846994</v>
       </c>
       <c r="H3">
-        <v>0.02546153846153846</v>
+        <v>0.05224043715846994</v>
       </c>
       <c r="I3">
-        <v>0.09769230769230769</v>
+        <v>-0.06502732240437158</v>
       </c>
       <c r="J3">
-        <v>0.09769230769230769</v>
+        <v>-0.06502732240437158</v>
       </c>
       <c r="K3">
-        <v>1.27</v>
+        <v>-1.19</v>
       </c>
       <c r="L3">
-        <v>0.09769230769230769</v>
+        <v>-0.06502732240437158</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,7 +737,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,37 +746,37 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="V3">
-        <v>0.06060606060606061</v>
+        <v>0.05918367346938776</v>
       </c>
       <c r="W3">
-        <v>0.03802395209580839</v>
+        <v>-0.03573573573573573</v>
       </c>
       <c r="X3">
-        <v>0.09310506888394895</v>
+        <v>0.08022808610603696</v>
       </c>
       <c r="Y3">
-        <v>-0.05508111678814057</v>
+        <v>-0.1159638218417727</v>
       </c>
       <c r="Z3">
-        <v>0.4696531791907514</v>
+        <v>0.6079734219269104</v>
       </c>
       <c r="AA3">
-        <v>0.04588150289017341</v>
+        <v>-0.03953488372093023</v>
       </c>
       <c r="AB3">
-        <v>0.09310506888394895</v>
+        <v>0.08022808610603696</v>
       </c>
       <c r="AC3">
-        <v>-0.04722356599377554</v>
+        <v>-0.1197629698269672</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-3.2</v>
+        <v>-3.19</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -797,10 +797,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.06451612903225808</v>
+        <v>-0.06290672451193058</v>
       </c>
       <c r="AK3">
-        <v>-0.106312292358804</v>
+        <v>-0.1080989495086411</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -809,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AP3">
-        <v>-2.388059701492537</v>
+        <v>2.981308411214953</v>
       </c>
     </row>
     <row r="4">
@@ -832,25 +832,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.009689999999999999</v>
+        <v>-0.0924</v>
       </c>
       <c r="G4">
-        <v>-0.006332082551594747</v>
+        <v>0.02183098591549296</v>
       </c>
       <c r="H4">
-        <v>-0.006332082551594747</v>
+        <v>0.02183098591549296</v>
       </c>
       <c r="I4">
-        <v>-0.01815811284909103</v>
+        <v>-0.2362488594756488</v>
       </c>
       <c r="J4">
-        <v>-0.01815811284909103</v>
+        <v>-0.2362488594756488</v>
       </c>
       <c r="K4">
-        <v>-2.13</v>
+        <v>-13.1</v>
       </c>
       <c r="L4">
-        <v>-0.0199812382739212</v>
+        <v>-0.2306338028169014</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -874,55 +874,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>9.49</v>
+        <v>13</v>
       </c>
       <c r="V4">
-        <v>0.3937759336099585</v>
+        <v>0.8125</v>
       </c>
       <c r="W4">
-        <v>-0.07220338983050847</v>
+        <v>-0.4145569620253164</v>
       </c>
       <c r="X4">
-        <v>0.1045480575747966</v>
+        <v>0.08041194153980047</v>
       </c>
       <c r="Y4">
-        <v>-0.1767514474053051</v>
+        <v>-0.4949689035651169</v>
       </c>
       <c r="Z4">
-        <v>11.31842185929957</v>
+        <v>2.084046048104781</v>
       </c>
       <c r="AA4">
-        <v>-0.2055211813947803</v>
+        <v>-0.4923535019594876</v>
       </c>
       <c r="AB4">
-        <v>0.0969757690697219</v>
+        <v>0.08018701271276529</v>
       </c>
       <c r="AC4">
-        <v>-0.3024969504645023</v>
+        <v>-0.5725405146722529</v>
       </c>
       <c r="AD4">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>0.02827414856551929</v>
+        <v>0.09467609108425908</v>
       </c>
       <c r="AF4">
-        <v>5.078274148565519</v>
+        <v>0.09467609108425908</v>
       </c>
       <c r="AG4">
-        <v>-4.411725851434481</v>
+        <v>-12.90532390891574</v>
       </c>
       <c r="AH4">
-        <v>0.1740429924919045</v>
+        <v>0.005882447745357575</v>
       </c>
       <c r="AI4">
-        <v>0.1384545556313786</v>
+        <v>0.0114693889911098</v>
       </c>
       <c r="AJ4">
-        <v>-0.2240788511041694</v>
+        <v>-4.170169519871849</v>
       </c>
       <c r="AK4">
-        <v>-0.1622657557198145</v>
+        <v>2.719587568020089</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -931,10 +931,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-5</v>
+        <v>-0</v>
       </c>
       <c r="AP4">
-        <v>4.368045397459882</v>
+        <v>0.9630838737996821</v>
       </c>
     </row>
   </sheetData>
